--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EA6362-AA85-41AC-9937-CB2B81025761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF1C19E-E781-4B8A-8C62-0C5AD1D5B4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-23940" yWindow="-360" windowWidth="21600" windowHeight="11180" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Subject,Predicate,Object</t>
+  </si>
+  <si>
+    <t>2,2,3,3,2,2,3,3,1</t>
   </si>
 </sst>
 </file>
@@ -139,7 +142,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -459,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -507,12 +510,23 @@
     </row>
     <row r="4" spans="1:4">
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
     </row>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF1C19E-E781-4B8A-8C62-0C5AD1D5B4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8FF4B1-2B7C-4E47-9982-AA92CA72A1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23940" yWindow="-360" windowWidth="21600" windowHeight="11180" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,13 @@
     <t>1,2,3,1,2,3,1,2,3,3,3</t>
   </si>
   <si>
-    <t>(list#sep=,);Enum.CheeseWord</t>
-  </si>
-  <si>
     <t>Subject,Predicate,Object</t>
   </si>
   <si>
     <t>2,2,3,3,2,2,3,3,1</t>
+  </si>
+  <si>
+    <t>(list#sep=,);Enum.CheeseWordData</t>
   </si>
 </sst>
 </file>
@@ -466,7 +466,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
@@ -494,7 +494,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="3" customFormat="1">
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8FF4B1-2B7C-4E47-9982-AA92CA72A1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A844EE-FF12-4EA1-BF1F-A79D4A33AEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4515" yWindow="5415" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,6 +72,21 @@
   </si>
   <si>
     <t>(list#sep=,);Enum.CheeseWordData</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>What do we name our kid?</t>
+  </si>
+  <si>
+    <t>Subject, Subject</t>
+  </si>
+  <si>
+    <t>4,5,6,7</t>
   </si>
 </sst>
 </file>
@@ -166,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +224,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -312,7 +330,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -462,14 +480,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +501,11 @@
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1">
+    <row r="2" spans="1:5" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -496,8 +518,11 @@
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1">
+    <row r="3" spans="1:5" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -508,7 +533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="B4">
         <v>0</v>
       </c>
@@ -519,7 +544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="B5">
         <v>1</v>
       </c>
@@ -528,6 +553,20 @@
       </c>
       <c r="D5" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A844EE-FF12-4EA1-BF1F-A79D4A33AEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E16F1F9-29B6-484F-B6B7-F06FC846F5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4515" yWindow="5415" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="46005" yWindow="7380" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,7 +86,25 @@
     <t>Subject, Subject</t>
   </si>
   <si>
-    <t>4,5,6,7</t>
+    <t>4,5,6,7,8,9,10,11</t>
+  </si>
+  <si>
+    <t>What do you want for dinner?</t>
+  </si>
+  <si>
+    <t>Adjective, Object</t>
+  </si>
+  <si>
+    <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
+  </si>
+  <si>
+    <t>What is your favorite memory of our early dating days?</t>
+  </si>
+  <si>
+    <t>Verb, Object</t>
+  </si>
+  <si>
+    <t>24,25,26,27,28,29,30,31,32</t>
   </si>
 </sst>
 </file>
@@ -480,12 +498,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
     <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -569,6 +587,34 @@
         <v>15</v>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E16F1F9-29B6-484F-B6B7-F06FC846F5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C902F-6CFE-4AD1-8256-03706AC4C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46005" yWindow="7380" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-25710" yWindow="-1210" windowWidth="25820" windowHeight="15500" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,12 +62,6 @@
     <t>1,2,3,1,2,3,1,2,3,3,3</t>
   </si>
   <si>
-    <t>Subject,Predicate,Object</t>
-  </si>
-  <si>
-    <t>2,2,3,3,2,2,3,3,1</t>
-  </si>
-  <si>
     <t>(list#sep=,);Enum.CheeseWordData</t>
   </si>
   <si>
@@ -83,28 +74,31 @@
     <t>What do we name our kid?</t>
   </si>
   <si>
-    <t>Subject, Subject</t>
-  </si>
-  <si>
     <t>4,5,6,7,8,9,10,11</t>
   </si>
   <si>
     <t>What do you want for dinner?</t>
   </si>
   <si>
-    <t>Adjective, Object</t>
-  </si>
-  <si>
     <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
   </si>
   <si>
     <t>What is your favorite memory of our early dating days?</t>
   </si>
   <si>
-    <t>Verb, Object</t>
-  </si>
-  <si>
     <t>24,25,26,27,28,29,30,31,32</t>
+  </si>
+  <si>
+    <t>Adjective,Object</t>
+  </si>
+  <si>
+    <t>Verb,Object</t>
+  </si>
+  <si>
+    <t>Subject,Subject</t>
+  </si>
+  <si>
+    <t>Subject</t>
   </si>
 </sst>
 </file>
@@ -202,9 +196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -242,7 +236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -348,7 +342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,7 +484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -498,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
@@ -520,7 +514,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1">
@@ -534,10 +528,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1">
@@ -559,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -567,10 +561,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -578,10 +575,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -592,27 +589,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C902F-6CFE-4AD1-8256-03706AC4C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C094F9F-16BC-456D-AEA4-64A5275E950C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-1210" windowWidth="25820" windowHeight="15500" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="36705" yWindow="7770" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -80,15 +83,9 @@
     <t>What do you want for dinner?</t>
   </si>
   <si>
-    <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-  </si>
-  <si>
     <t>What is your favorite memory of our early dating days?</t>
   </si>
   <si>
-    <t>24,25,26,27,28,29,30,31,32</t>
-  </si>
-  <si>
     <t>Adjective,Object</t>
   </si>
   <si>
@@ -99,6 +96,12 @@
   </si>
   <si>
     <t>Subject</t>
+  </si>
+  <si>
+    <t>12,13,14,15,16,17,18,19,20,21</t>
+  </si>
+  <si>
+    <t>22,23,24,25,26,27,28,29,30</t>
   </si>
 </sst>
 </file>
@@ -196,9 +199,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -236,7 +239,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -342,7 +345,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,7 +487,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -553,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -564,7 +567,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -575,10 +578,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -589,13 +592,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C094F9F-16BC-456D-AEA4-64A5275E950C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E83764-3BC2-4D1B-85B4-D53CFC7A7DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36705" yWindow="7770" windowWidth="28800" windowHeight="15885" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="16440" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <t>12,13,14,15,16,17,18,19,20,21</t>
   </si>
   <si>
-    <t>22,23,24,25,26,27,28,29,30</t>
+    <t>22,23,24,25,26,27,28</t>
   </si>
 </sst>
 </file>

--- a/XmlData/Datas/cheeseScene.xlsx
+++ b/XmlData/Datas/cheeseScene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E83764-3BC2-4D1B-85B4-D53CFC7A7DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892731C3-90AE-47D0-9C9B-349B355F988D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="16440" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,16 +89,16 @@
     <t>Verb,Object</t>
   </si>
   <si>
-    <t>Subject,Subject</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
-    <t>12,13,14,15,16,17,18,19,20,21</t>
-  </si>
-  <si>
-    <t>22,23,24,25,26,27,28</t>
+    <t>Test question</t>
+  </si>
+  <si>
+    <t>12,13,14,15,16</t>
+  </si>
+  <si>
+    <t>17,18,19</t>
   </si>
 </sst>
 </file>
@@ -199,9 +196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -239,7 +236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -345,7 +342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -487,7 +484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -556,6 +553,9 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
     </row>
